--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -475,11 +475,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>2024</v>
       </c>
@@ -489,11 +485,7 @@
       <c r="E2" t="n">
         <v>238</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -501,11 +493,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>2024</v>
       </c>
@@ -515,11 +503,7 @@
       <c r="E3" t="n">
         <v>158</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -527,11 +511,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>2024</v>
       </c>
@@ -541,11 +521,7 @@
       <c r="E4" t="n">
         <v>135</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -553,11 +529,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>2024</v>
       </c>
@@ -567,11 +539,7 @@
       <c r="E5" t="n">
         <v>107</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -579,11 +547,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>2024</v>
       </c>
@@ -593,11 +557,7 @@
       <c r="E6" t="n">
         <v>50</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -605,11 +565,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>2024</v>
       </c>
@@ -619,11 +575,7 @@
       <c r="E7" t="n">
         <v>227</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -631,11 +583,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>2024</v>
       </c>
@@ -645,11 +593,7 @@
       <c r="E8" t="n">
         <v>115</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -657,11 +601,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>2024</v>
       </c>
@@ -671,11 +611,7 @@
       <c r="E9" t="n">
         <v>223</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -683,11 +619,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>2024</v>
       </c>
@@ -697,11 +629,7 @@
       <c r="E10" t="n">
         <v>224</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -709,11 +637,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>2024</v>
       </c>
@@ -723,11 +647,7 @@
       <c r="E11" t="n">
         <v>204</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -735,11 +655,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>2024</v>
       </c>
@@ -749,11 +665,7 @@
       <c r="E12" t="n">
         <v>173</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -761,11 +673,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>2024</v>
       </c>
@@ -775,11 +683,7 @@
       <c r="E13" t="n">
         <v>264</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -787,11 +691,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>2025</v>
       </c>
@@ -801,11 +701,7 @@
       <c r="E14" t="n">
         <v>371</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -813,11 +709,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>2025</v>
       </c>
@@ -827,11 +719,7 @@
       <c r="E15" t="n">
         <v>371</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -839,11 +727,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>2025</v>
       </c>
@@ -853,11 +737,7 @@
       <c r="E16" t="n">
         <v>227</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -865,11 +745,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>2025</v>
       </c>
@@ -879,11 +755,7 @@
       <c r="E17" t="n">
         <v>232</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -891,11 +763,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>2025</v>
       </c>
@@ -905,11 +773,7 @@
       <c r="E18" t="n">
         <v>261</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -917,11 +781,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>2025</v>
       </c>
@@ -931,11 +791,7 @@
       <c r="E19" t="n">
         <v>129</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -943,11 +799,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>2025</v>
       </c>
@@ -957,11 +809,7 @@
       <c r="E20" t="n">
         <v>186</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -969,11 +817,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>2025</v>
       </c>
@@ -983,11 +827,7 @@
       <c r="E21" t="n">
         <v>194</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -995,11 +835,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>2025</v>
       </c>
@@ -1009,11 +845,7 @@
       <c r="E22" t="n">
         <v>195</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1021,11 +853,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>2025</v>
       </c>
@@ -1035,11 +863,7 @@
       <c r="E23" t="n">
         <v>175</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1047,11 +871,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>2025</v>
       </c>
@@ -1061,11 +881,7 @@
       <c r="E24" t="n">
         <v>178</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1073,11 +889,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>2025</v>
       </c>
@@ -1087,11 +899,7 @@
       <c r="E25" t="n">
         <v>152</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1099,11 +907,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>2026</v>
       </c>
@@ -1113,11 +917,7 @@
       <c r="E26" t="n">
         <v>250</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1125,11 +925,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>2026</v>
       </c>
@@ -1139,11 +935,7 @@
       <c r="E27" t="n">
         <v>157</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1151,11 +943,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>2026</v>
       </c>
@@ -1165,11 +953,7 @@
       <c r="E28" t="n">
         <v>216</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1177,11 +961,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>2026</v>
       </c>
@@ -1191,11 +971,7 @@
       <c r="E29" t="n">
         <v>182</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1203,11 +979,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>2026</v>
       </c>
@@ -1217,11 +989,7 @@
       <c r="E30" t="n">
         <v>212</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1229,11 +997,7 @@
           <t>Aldeota</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>2026</v>
       </c>
@@ -1243,11 +1007,7 @@
       <c r="E31" t="n">
         <v>202</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-07-07 09:53</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1267,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -1833,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -2399,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3295,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -4097,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4427,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -5229,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -5795,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -6361,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6691,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -7497,7 +7257,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -8059,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -8625,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -9195,7 +8955,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -9757,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -10323,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10653,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11219,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -12025,7 +11785,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -12587,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -13157,7 +12917,7 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -13719,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -14285,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-07 09:53</t>
+          <t>2026-07-07 14:36</t>
         </is>
       </c>
     </row>
@@ -14510,97 +14270,97 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3">
@@ -14700,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>201</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4">
@@ -14800,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5">
@@ -14900,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -15000,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>645</v>
+        <v>677</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -11219,7 +11219,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-07 14:36</t>
+          <t>2026-07-07 16:16</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>677</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1031,7 +1031,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -11219,7 +11219,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -12917,7 +12917,7 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-07 16:16</t>
+          <t>2026-07-07 16:23</t>
         </is>
       </c>
     </row>
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-07 16:23</t>
+          <t>2026-07-08 13:17</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>256</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>223</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>178</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>695</v>
+        <v>782</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -11219,7 +11219,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-08 13:17</t>
+          <t>2026-07-09 10:39</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>285</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>250</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>198</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>782</v>
+        <v>953</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -11219,7 +11219,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -12917,7 +12917,7 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-09 10:39</t>
+          <t>2026-07-09 11:32</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>953</v>
+        <v>962</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1031,7 +1031,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -11219,7 +11219,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -12917,7 +12917,7 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-09 11:32</t>
+          <t>2026-07-09 11:41</t>
         </is>
       </c>
     </row>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1031,7 +1031,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -11219,7 +11219,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -12917,7 +12917,7 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-09 11:41</t>
+          <t>2026-07-09 11:50</t>
         </is>
       </c>
     </row>
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -11219,7 +11219,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -12917,7 +12917,7 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-09 11:50</t>
+          <t>2026-07-09 14:33</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>963</v>
+        <v>981</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-09 14:33</t>
+          <t>2026-07-10 14:09</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>357</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>330</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>232</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>981</v>
+        <v>1121</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-10 14:09</t>
+          <t>2026-07-11 11:37</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>401</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>391</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>256</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>1121</v>
+        <v>1216</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-11 11:37</t>
+          <t>2026-07-12 11:40</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>432</v>
+        <v>445</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>423</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>277</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>1216</v>
+        <v>1267</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-12 11:40</t>
+          <t>2026-07-13 14:37</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>445</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>440</v>
+        <v>489</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>290</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>1267</v>
+        <v>1395</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-13 14:37</t>
+          <t>2026-07-14 12:16</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>481</v>
+        <v>520</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>489</v>
+        <v>546</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>320</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>1395</v>
+        <v>1559</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-14 12:16</t>
+          <t>2026-07-15 12:15</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>520</v>
+        <v>571</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>546</v>
+        <v>591</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>376</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>1559</v>
+        <v>1708</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-15 12:15</t>
+          <t>2026-07-16 12:51</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>571</v>
+        <v>620</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>591</v>
+        <v>647</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>419</v>
+        <v>448</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>127</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>1708</v>
+        <v>1906</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-16 12:51</t>
+          <t>2026-07-17 12:02</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>620</v>
+        <v>658</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>647</v>
+        <v>707</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>448</v>
+        <v>478</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>191</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>1906</v>
+        <v>2072</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-17 12:02</t>
+          <t>2026-07-18 09:43</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>658</v>
+        <v>692</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>707</v>
+        <v>735</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>478</v>
+        <v>504</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>229</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>2072</v>
+        <v>2186</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-18 09:43</t>
+          <t>2026-07-19 11:38</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>692</v>
+        <v>714</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>735</v>
+        <v>757</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>504</v>
+        <v>528</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>255</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>2186</v>
+        <v>2296</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-19 11:38</t>
+          <t>2026-07-20 13:11</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>714</v>
+        <v>752</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>757</v>
+        <v>783</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>528</v>
+        <v>548</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>297</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>2296</v>
+        <v>2428</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-20 13:11</t>
+          <t>2026-07-21 12:58</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>752</v>
+        <v>809</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>783</v>
+        <v>849</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>548</v>
+        <v>589</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>345</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>2428</v>
+        <v>2625</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-21 12:58</t>
+          <t>2026-07-22 12:54</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>809</v>
+        <v>850</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>849</v>
+        <v>909</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>589</v>
+        <v>624</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>378</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>2625</v>
+        <v>2801</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-22 12:54</t>
+          <t>2026-07-23 13:08</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>850</v>
+        <v>908</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>909</v>
+        <v>962</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>624</v>
+        <v>663</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>418</v>
+        <v>448</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>2801</v>
+        <v>2981</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-23 13:08</t>
+          <t>2026-07-24 12:19</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>908</v>
+        <v>956</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>962</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>663</v>
+        <v>696</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>448</v>
+        <v>492</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>2981</v>
+        <v>3174</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-24 12:19</t>
+          <t>2026-07-25 11:48</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>956</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1030</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>696</v>
+        <v>722</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>492</v>
+        <v>537</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>3174</v>
+        <v>3353</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1031,7 +1031,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -12917,7 +12917,7 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-25 11:48</t>
+          <t>2026-07-26 11:50</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1001</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1093</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>722</v>
+        <v>735</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>537</v>
+        <v>579</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>3353</v>
+        <v>3443</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-26 11:50</t>
+          <t>2026-07-27 14:14</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1023</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1106</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>735</v>
+        <v>761</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>579</v>
+        <v>621</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>3443</v>
+        <v>3581</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-27 14:14</t>
+          <t>2026-07-28 13:25</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1066</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1133</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>761</v>
+        <v>783</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>621</v>
+        <v>651</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>3581</v>
+        <v>3743</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-28 13:25</t>
+          <t>2026-07-29 13:03</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1127</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1182</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>783</v>
+        <v>833</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>651</v>
+        <v>695</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>3743</v>
+        <v>3949</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-29 13:03</t>
+          <t>2026-07-30 13:07</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1173</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1248</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>833</v>
+        <v>855</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>695</v>
+        <v>737</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>3949</v>
+        <v>4121</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1027,11 +1027,11 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -1593,11 +1593,11 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2159,11 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -3291,11 +3291,11 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -4989,11 +4989,11 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -5555,11 +5555,11 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         <v>7</v>
       </c>
       <c r="E342" t="n">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -7253,11 +7253,11 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -7819,11 +7819,11 @@
         <v>7</v>
       </c>
       <c r="E404" t="n">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -8951,11 +8951,11 @@
         <v>7</v>
       </c>
       <c r="E466" t="n">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -9517,11 +9517,11 @@
         <v>7</v>
       </c>
       <c r="E497" t="n">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -10083,11 +10083,11 @@
         <v>7</v>
       </c>
       <c r="E528" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -10649,11 +10649,11 @@
         <v>7</v>
       </c>
       <c r="E559" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -11215,11 +11215,11 @@
         <v>7</v>
       </c>
       <c r="E590" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11781,11 @@
         <v>7</v>
       </c>
       <c r="E621" t="n">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -12347,11 +12347,11 @@
         <v>7</v>
       </c>
       <c r="E652" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v>7</v>
       </c>
       <c r="E683" t="n">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -13479,11 +13479,11 @@
         <v>7</v>
       </c>
       <c r="E714" t="n">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -14045,11 +14045,11 @@
         <v>7</v>
       </c>
       <c r="E745" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2026-07-30 13:07</t>
+          <t>2026-07-31 13:23</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1218</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="3">
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1311</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="4">
@@ -14560,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>855</v>
+        <v>905</v>
       </c>
     </row>
     <row r="5">
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>737</v>
+        <v>776</v>
       </c>
     </row>
     <row r="6">
@@ -14760,7 +14760,7 @@
         <v>2818</v>
       </c>
       <c r="AF6" t="n">
-        <v>4121</v>
+        <v>4326</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -10977,7 +10977,7 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -12145,7 +12145,7 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-01 11:44</t>
+          <t>2026-08-02 08:12</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>42</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-02 08:12</t>
+          <t>2026-08-03 09:49</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>103</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-03 09:49</t>
+          <t>2026-08-04 08:57</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>55</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>54</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>41</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>88</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>238</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-04 08:57</t>
+          <t>2026-08-05 08:51</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>106</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>124</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>81</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>124</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>435</v>
+        <v>621</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-05 08:51</t>
+          <t>2026-08-06 08:56</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>161</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>171</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>130</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>159</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>621</v>
+        <v>764</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-06 08:56</t>
+          <t>2026-08-07 07:42</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>204</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>199</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>172</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>189</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>764</v>
+        <v>914</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-07 07:42</t>
+          <t>2026-08-08 07:21</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>245</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>241</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>218</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>914</v>
+        <v>1056</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-08 07:21</t>
+          <t>2026-08-09 07:23</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>286</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>285</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>253</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>1056</v>
+        <v>1127</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-09 07:23</t>
+          <t>2026-08-10 07:59</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>303</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>311</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>239</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>274</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>1127</v>
+        <v>1203</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-10 07:59</t>
+          <t>2026-08-11 07:43</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>319</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>336</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>258</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>290</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>1203</v>
+        <v>1401</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-11 07:43</t>
+          <t>2026-08-12 07:51</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>365</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>406</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>308</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>322</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>1401</v>
+        <v>1534</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-12 07:51</t>
+          <t>2026-08-13 07:51</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>399</v>
+        <v>443</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>453</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>332</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>350</v>
+        <v>386</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>1534</v>
+        <v>1698</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-13 07:51</t>
+          <t>2026-08-14 07:47</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>443</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>512</v>
+        <v>563</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>357</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>386</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>1698</v>
+        <v>1842</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-14 07:47</t>
+          <t>2026-08-15 07:12</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>480</v>
+        <v>521</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>563</v>
+        <v>609</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>383</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>416</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>1842</v>
+        <v>1979</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -10977,7 +10977,7 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-15 07:12</t>
+          <t>2026-08-16 07:13</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>521</v>
+        <v>542</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>609</v>
+        <v>621</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>405</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>444</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>1979</v>
+        <v>2075</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-16 07:13</t>
+          <t>2026-08-17 07:21</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>542</v>
+        <v>557</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>621</v>
+        <v>653</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>426</v>
+        <v>440</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>486</v>
+        <v>515</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>2075</v>
+        <v>2165</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-17 07:21</t>
+          <t>2026-08-18 07:18</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>557</v>
+        <v>614</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>653</v>
+        <v>716</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>440</v>
+        <v>483</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>515</v>
+        <v>561</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>2165</v>
+        <v>2374</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-18 07:18</t>
+          <t>2026-08-19 07:23</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>614</v>
+        <v>650</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>716</v>
+        <v>772</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>483</v>
+        <v>510</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>561</v>
+        <v>595</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>2374</v>
+        <v>2527</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-19 07:23</t>
+          <t>2026-08-20 07:19</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>650</v>
+        <v>690</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>772</v>
+        <v>829</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>510</v>
+        <v>543</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>595</v>
+        <v>635</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>2527</v>
+        <v>2697</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-20 07:19</t>
+          <t>2026-08-21 07:19</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>690</v>
+        <v>738</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>829</v>
+        <v>865</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>543</v>
+        <v>563</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>635</v>
+        <v>687</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>2697</v>
+        <v>2853</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-21 07:19</t>
+          <t>2026-08-22 07:12</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>738</v>
+        <v>783</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>865</v>
+        <v>919</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>563</v>
+        <v>582</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>687</v>
+        <v>740</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>2853</v>
+        <v>3024</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B642" t="inlineStr"/>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C642" t="n">
         <v>2024</v>
       </c>
@@ -12165,7 +12169,11 @@
       <c r="E642" t="n">
         <v>156</v>
       </c>
-      <c r="F642" t="inlineStr"/>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -12173,7 +12181,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B643" t="inlineStr"/>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C643" t="n">
         <v>2024</v>
       </c>
@@ -12183,7 +12195,11 @@
       <c r="E643" t="n">
         <v>94</v>
       </c>
-      <c r="F643" t="inlineStr"/>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -12191,7 +12207,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B644" t="inlineStr"/>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C644" t="n">
         <v>2024</v>
       </c>
@@ -12201,7 +12221,11 @@
       <c r="E644" t="n">
         <v>113</v>
       </c>
-      <c r="F644" t="inlineStr"/>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -12209,7 +12233,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B645" t="inlineStr"/>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C645" t="n">
         <v>2024</v>
       </c>
@@ -12219,7 +12247,11 @@
       <c r="E645" t="n">
         <v>94</v>
       </c>
-      <c r="F645" t="inlineStr"/>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -12227,7 +12259,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B646" t="inlineStr"/>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C646" t="n">
         <v>2024</v>
       </c>
@@ -12237,7 +12273,11 @@
       <c r="E646" t="n">
         <v>87</v>
       </c>
-      <c r="F646" t="inlineStr"/>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -12245,7 +12285,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B647" t="inlineStr"/>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C647" t="n">
         <v>2024</v>
       </c>
@@ -12255,7 +12299,11 @@
       <c r="E647" t="n">
         <v>85</v>
       </c>
-      <c r="F647" t="inlineStr"/>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -12263,7 +12311,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B648" t="inlineStr"/>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C648" t="n">
         <v>2024</v>
       </c>
@@ -12273,7 +12325,11 @@
       <c r="E648" t="n">
         <v>60</v>
       </c>
-      <c r="F648" t="inlineStr"/>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -12281,7 +12337,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B649" t="inlineStr"/>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C649" t="n">
         <v>2024</v>
       </c>
@@ -12291,7 +12351,11 @@
       <c r="E649" t="n">
         <v>92</v>
       </c>
-      <c r="F649" t="inlineStr"/>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -12299,7 +12363,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B650" t="inlineStr"/>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C650" t="n">
         <v>2024</v>
       </c>
@@ -12309,7 +12377,11 @@
       <c r="E650" t="n">
         <v>95</v>
       </c>
-      <c r="F650" t="inlineStr"/>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -12317,7 +12389,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B651" t="inlineStr"/>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C651" t="n">
         <v>2024</v>
       </c>
@@ -12327,7 +12403,11 @@
       <c r="E651" t="n">
         <v>106</v>
       </c>
-      <c r="F651" t="inlineStr"/>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -12335,7 +12415,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B652" t="inlineStr"/>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C652" t="n">
         <v>2024</v>
       </c>
@@ -12345,7 +12429,11 @@
       <c r="E652" t="n">
         <v>68</v>
       </c>
-      <c r="F652" t="inlineStr"/>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -12353,7 +12441,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B653" t="inlineStr"/>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C653" t="n">
         <v>2024</v>
       </c>
@@ -12363,7 +12455,11 @@
       <c r="E653" t="n">
         <v>116</v>
       </c>
-      <c r="F653" t="inlineStr"/>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -12371,7 +12467,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B654" t="inlineStr"/>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C654" t="n">
         <v>2025</v>
       </c>
@@ -12381,7 +12481,11 @@
       <c r="E654" t="n">
         <v>210</v>
       </c>
-      <c r="F654" t="inlineStr"/>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -12389,7 +12493,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B655" t="inlineStr"/>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C655" t="n">
         <v>2025</v>
       </c>
@@ -12399,7 +12507,11 @@
       <c r="E655" t="n">
         <v>144</v>
       </c>
-      <c r="F655" t="inlineStr"/>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -12407,7 +12519,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B656" t="inlineStr"/>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C656" t="n">
         <v>2025</v>
       </c>
@@ -12417,7 +12533,11 @@
       <c r="E656" t="n">
         <v>131</v>
       </c>
-      <c r="F656" t="inlineStr"/>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -12425,7 +12545,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B657" t="inlineStr"/>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C657" t="n">
         <v>2025</v>
       </c>
@@ -12435,7 +12559,11 @@
       <c r="E657" t="n">
         <v>101</v>
       </c>
-      <c r="F657" t="inlineStr"/>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -12443,7 +12571,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B658" t="inlineStr"/>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C658" t="n">
         <v>2025</v>
       </c>
@@ -12453,7 +12585,11 @@
       <c r="E658" t="n">
         <v>133</v>
       </c>
-      <c r="F658" t="inlineStr"/>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -12461,7 +12597,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B659" t="inlineStr"/>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C659" t="n">
         <v>2025</v>
       </c>
@@ -12471,7 +12611,11 @@
       <c r="E659" t="n">
         <v>89</v>
       </c>
-      <c r="F659" t="inlineStr"/>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -12479,7 +12623,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B660" t="inlineStr"/>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C660" t="n">
         <v>2025</v>
       </c>
@@ -12489,7 +12637,11 @@
       <c r="E660" t="n">
         <v>90</v>
       </c>
-      <c r="F660" t="inlineStr"/>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -12497,7 +12649,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B661" t="inlineStr"/>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C661" t="n">
         <v>2025</v>
       </c>
@@ -12507,7 +12663,11 @@
       <c r="E661" t="n">
         <v>148</v>
       </c>
-      <c r="F661" t="inlineStr"/>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -12515,7 +12675,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B662" t="inlineStr"/>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C662" t="n">
         <v>2025</v>
       </c>
@@ -12525,7 +12689,11 @@
       <c r="E662" t="n">
         <v>102</v>
       </c>
-      <c r="F662" t="inlineStr"/>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -12533,7 +12701,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B663" t="inlineStr"/>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C663" t="n">
         <v>2025</v>
       </c>
@@ -12543,7 +12715,11 @@
       <c r="E663" t="n">
         <v>101</v>
       </c>
-      <c r="F663" t="inlineStr"/>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -12551,7 +12727,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B664" t="inlineStr"/>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C664" t="n">
         <v>2025</v>
       </c>
@@ -12561,7 +12741,11 @@
       <c r="E664" t="n">
         <v>79</v>
       </c>
-      <c r="F664" t="inlineStr"/>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -12569,7 +12753,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B665" t="inlineStr"/>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C665" t="n">
         <v>2025</v>
       </c>
@@ -12579,7 +12767,11 @@
       <c r="E665" t="n">
         <v>106</v>
       </c>
-      <c r="F665" t="inlineStr"/>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -12587,7 +12779,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B666" t="inlineStr"/>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C666" t="n">
         <v>2026</v>
       </c>
@@ -12597,7 +12793,11 @@
       <c r="E666" t="n">
         <v>173</v>
       </c>
-      <c r="F666" t="inlineStr"/>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -12605,7 +12805,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B667" t="inlineStr"/>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C667" t="n">
         <v>2026</v>
       </c>
@@ -12615,7 +12819,11 @@
       <c r="E667" t="n">
         <v>98</v>
       </c>
-      <c r="F667" t="inlineStr"/>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -12623,7 +12831,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B668" t="inlineStr"/>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C668" t="n">
         <v>2026</v>
       </c>
@@ -12633,7 +12845,11 @@
       <c r="E668" t="n">
         <v>114</v>
       </c>
-      <c r="F668" t="inlineStr"/>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -12641,7 +12857,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B669" t="inlineStr"/>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C669" t="n">
         <v>2026</v>
       </c>
@@ -12651,7 +12871,11 @@
       <c r="E669" t="n">
         <v>85</v>
       </c>
-      <c r="F669" t="inlineStr"/>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -12659,7 +12883,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B670" t="inlineStr"/>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C670" t="n">
         <v>2026</v>
       </c>
@@ -12669,7 +12897,11 @@
       <c r="E670" t="n">
         <v>78</v>
       </c>
-      <c r="F670" t="inlineStr"/>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -12677,7 +12909,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B671" t="inlineStr"/>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C671" t="n">
         <v>2026</v>
       </c>
@@ -12687,7 +12923,11 @@
       <c r="E671" t="n">
         <v>82</v>
       </c>
-      <c r="F671" t="inlineStr"/>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -12695,7 +12935,11 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B672" t="inlineStr"/>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Regiao 1</t>
+        </is>
+      </c>
       <c r="C672" t="n">
         <v>2026</v>
       </c>
@@ -12705,7 +12949,11 @@
       <c r="E672" t="n">
         <v>123</v>
       </c>
-      <c r="F672" t="inlineStr"/>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:14</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -12729,7 +12977,7 @@
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13557,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -13893,11 +14141,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14725,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-22 07:12</t>
+          <t>2026-08-23 07:14</t>
         </is>
       </c>
     </row>
@@ -14708,100 +14956,100 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="AG2" t="n">
-        <v>783</v>
+        <v>798</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +15152,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>919</v>
+        <v>944</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15255,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>582</v>
+        <v>593</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15358,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>740</v>
+        <v>785</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15461,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>3024</v>
+        <v>3120</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -12155,11 +12155,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B642" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B642" t="inlineStr"/>
       <c r="C642" t="n">
         <v>2024</v>
       </c>
@@ -12169,11 +12165,7 @@
       <c r="E642" t="n">
         <v>156</v>
       </c>
-      <c r="F642" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -12181,11 +12173,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B643" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B643" t="inlineStr"/>
       <c r="C643" t="n">
         <v>2024</v>
       </c>
@@ -12195,11 +12183,7 @@
       <c r="E643" t="n">
         <v>94</v>
       </c>
-      <c r="F643" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -12207,11 +12191,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B644" t="inlineStr"/>
       <c r="C644" t="n">
         <v>2024</v>
       </c>
@@ -12221,11 +12201,7 @@
       <c r="E644" t="n">
         <v>113</v>
       </c>
-      <c r="F644" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -12233,11 +12209,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B645" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B645" t="inlineStr"/>
       <c r="C645" t="n">
         <v>2024</v>
       </c>
@@ -12247,11 +12219,7 @@
       <c r="E645" t="n">
         <v>94</v>
       </c>
-      <c r="F645" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -12259,11 +12227,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B646" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B646" t="inlineStr"/>
       <c r="C646" t="n">
         <v>2024</v>
       </c>
@@ -12273,11 +12237,7 @@
       <c r="E646" t="n">
         <v>87</v>
       </c>
-      <c r="F646" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -12285,11 +12245,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B647" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B647" t="inlineStr"/>
       <c r="C647" t="n">
         <v>2024</v>
       </c>
@@ -12299,11 +12255,7 @@
       <c r="E647" t="n">
         <v>85</v>
       </c>
-      <c r="F647" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -12311,11 +12263,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B648" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B648" t="inlineStr"/>
       <c r="C648" t="n">
         <v>2024</v>
       </c>
@@ -12325,11 +12273,7 @@
       <c r="E648" t="n">
         <v>60</v>
       </c>
-      <c r="F648" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -12337,11 +12281,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B649" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B649" t="inlineStr"/>
       <c r="C649" t="n">
         <v>2024</v>
       </c>
@@ -12351,11 +12291,7 @@
       <c r="E649" t="n">
         <v>92</v>
       </c>
-      <c r="F649" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -12363,11 +12299,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B650" t="inlineStr"/>
       <c r="C650" t="n">
         <v>2024</v>
       </c>
@@ -12377,11 +12309,7 @@
       <c r="E650" t="n">
         <v>95</v>
       </c>
-      <c r="F650" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -12389,11 +12317,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B651" t="inlineStr"/>
       <c r="C651" t="n">
         <v>2024</v>
       </c>
@@ -12403,11 +12327,7 @@
       <c r="E651" t="n">
         <v>106</v>
       </c>
-      <c r="F651" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -12415,11 +12335,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B652" t="inlineStr"/>
       <c r="C652" t="n">
         <v>2024</v>
       </c>
@@ -12429,11 +12345,7 @@
       <c r="E652" t="n">
         <v>68</v>
       </c>
-      <c r="F652" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -12441,11 +12353,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B653" t="inlineStr"/>
       <c r="C653" t="n">
         <v>2024</v>
       </c>
@@ -12455,11 +12363,7 @@
       <c r="E653" t="n">
         <v>116</v>
       </c>
-      <c r="F653" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -12467,11 +12371,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B654" t="inlineStr"/>
       <c r="C654" t="n">
         <v>2025</v>
       </c>
@@ -12481,11 +12381,7 @@
       <c r="E654" t="n">
         <v>210</v>
       </c>
-      <c r="F654" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F654" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -12493,11 +12389,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B655" t="inlineStr"/>
       <c r="C655" t="n">
         <v>2025</v>
       </c>
@@ -12507,11 +12399,7 @@
       <c r="E655" t="n">
         <v>144</v>
       </c>
-      <c r="F655" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -12519,11 +12407,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B656" t="inlineStr"/>
       <c r="C656" t="n">
         <v>2025</v>
       </c>
@@ -12533,11 +12417,7 @@
       <c r="E656" t="n">
         <v>131</v>
       </c>
-      <c r="F656" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -12545,11 +12425,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B657" t="inlineStr"/>
       <c r="C657" t="n">
         <v>2025</v>
       </c>
@@ -12559,11 +12435,7 @@
       <c r="E657" t="n">
         <v>101</v>
       </c>
-      <c r="F657" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -12571,11 +12443,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B658" t="inlineStr"/>
       <c r="C658" t="n">
         <v>2025</v>
       </c>
@@ -12585,11 +12453,7 @@
       <c r="E658" t="n">
         <v>133</v>
       </c>
-      <c r="F658" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -12597,11 +12461,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B659" t="inlineStr"/>
       <c r="C659" t="n">
         <v>2025</v>
       </c>
@@ -12611,11 +12471,7 @@
       <c r="E659" t="n">
         <v>89</v>
       </c>
-      <c r="F659" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -12623,11 +12479,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B660" t="inlineStr"/>
       <c r="C660" t="n">
         <v>2025</v>
       </c>
@@ -12637,11 +12489,7 @@
       <c r="E660" t="n">
         <v>90</v>
       </c>
-      <c r="F660" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -12649,11 +12497,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B661" t="inlineStr"/>
       <c r="C661" t="n">
         <v>2025</v>
       </c>
@@ -12663,11 +12507,7 @@
       <c r="E661" t="n">
         <v>148</v>
       </c>
-      <c r="F661" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F661" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -12675,11 +12515,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B662" t="inlineStr"/>
       <c r="C662" t="n">
         <v>2025</v>
       </c>
@@ -12689,11 +12525,7 @@
       <c r="E662" t="n">
         <v>102</v>
       </c>
-      <c r="F662" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -12701,11 +12533,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B663" t="inlineStr"/>
       <c r="C663" t="n">
         <v>2025</v>
       </c>
@@ -12715,11 +12543,7 @@
       <c r="E663" t="n">
         <v>101</v>
       </c>
-      <c r="F663" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F663" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -12727,11 +12551,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B664" t="inlineStr"/>
       <c r="C664" t="n">
         <v>2025</v>
       </c>
@@ -12741,11 +12561,7 @@
       <c r="E664" t="n">
         <v>79</v>
       </c>
-      <c r="F664" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F664" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -12753,11 +12569,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B665" t="inlineStr"/>
       <c r="C665" t="n">
         <v>2025</v>
       </c>
@@ -12767,11 +12579,7 @@
       <c r="E665" t="n">
         <v>106</v>
       </c>
-      <c r="F665" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -12779,11 +12587,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B666" t="inlineStr"/>
       <c r="C666" t="n">
         <v>2026</v>
       </c>
@@ -12793,11 +12597,7 @@
       <c r="E666" t="n">
         <v>173</v>
       </c>
-      <c r="F666" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -12805,11 +12605,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B667" t="inlineStr"/>
       <c r="C667" t="n">
         <v>2026</v>
       </c>
@@ -12819,11 +12615,7 @@
       <c r="E667" t="n">
         <v>98</v>
       </c>
-      <c r="F667" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F667" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -12831,11 +12623,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B668" t="inlineStr"/>
       <c r="C668" t="n">
         <v>2026</v>
       </c>
@@ -12845,11 +12633,7 @@
       <c r="E668" t="n">
         <v>114</v>
       </c>
-      <c r="F668" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -12857,11 +12641,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B669" t="inlineStr"/>
       <c r="C669" t="n">
         <v>2026</v>
       </c>
@@ -12871,11 +12651,7 @@
       <c r="E669" t="n">
         <v>85</v>
       </c>
-      <c r="F669" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -12883,11 +12659,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B670" t="inlineStr"/>
       <c r="C670" t="n">
         <v>2026</v>
       </c>
@@ -12897,11 +12669,7 @@
       <c r="E670" t="n">
         <v>78</v>
       </c>
-      <c r="F670" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F670" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -12909,11 +12677,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B671" t="inlineStr"/>
       <c r="C671" t="n">
         <v>2026</v>
       </c>
@@ -12923,11 +12687,7 @@
       <c r="E671" t="n">
         <v>82</v>
       </c>
-      <c r="F671" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -12935,11 +12695,7 @@
           <t>Rui Barbosa</t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
-        <is>
-          <t>Regiao 1</t>
-        </is>
-      </c>
+      <c r="B672" t="inlineStr"/>
       <c r="C672" t="n">
         <v>2026</v>
       </c>
@@ -12949,11 +12705,7 @@
       <c r="E672" t="n">
         <v>123</v>
       </c>
-      <c r="F672" t="inlineStr">
-        <is>
-          <t>2026-08-23 07:14</t>
-        </is>
-      </c>
+      <c r="F672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -12973,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -13557,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -14141,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -14725,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-23 07:14</t>
+          <t>2026-08-24 07:27</t>
         </is>
       </c>
     </row>
@@ -14956,100 +14708,100 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>798</v>
+        <v>822</v>
       </c>
     </row>
     <row r="3">
@@ -15152,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>944</v>
+        <v>968</v>
       </c>
     </row>
     <row r="4">
@@ -15255,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>593</v>
+        <v>606</v>
       </c>
     </row>
     <row r="5">
@@ -15358,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>785</v>
+        <v>824</v>
       </c>
     </row>
     <row r="6">
@@ -15461,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>3120</v>
+        <v>3220</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-24 07:27</t>
+          <t>2026-08-25 07:23</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>822</v>
+        <v>868</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>968</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>606</v>
+        <v>637</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>824</v>
+        <v>853</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>3220</v>
+        <v>3394</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-25 07:23</t>
+          <t>2026-08-26 07:25</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>868</v>
+        <v>904</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1036</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>637</v>
+        <v>675</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>853</v>
+        <v>890</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>3394</v>
+        <v>3561</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>463</v>
+        <v>493</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>383</v>
+        <v>415</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-26 07:25</t>
+          <t>2026-08-27 17:06</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>904</v>
+        <v>952</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1092</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>675</v>
+        <v>729</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>890</v>
+        <v>956</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>3561</v>
+        <v>3789</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-27 17:06</t>
+          <t>2026-08-28 18:03</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>952</v>
+        <v>986</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1152</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>729</v>
+        <v>767</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>956</v>
+        <v>997</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>3789</v>
+        <v>3942</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -10977,7 +10977,7 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -12145,7 +12145,7 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-28 18:03</t>
+          <t>2026-08-29 11:47</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>986</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1192</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>767</v>
+        <v>788</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>997</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>3942</v>
+        <v>4026</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-29 11:47</t>
+          <t>2026-08-30 11:36</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1004</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1206</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>788</v>
+        <v>798</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1028</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>4026</v>
+        <v>4111</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1045,11 +1045,11 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -1629,11 +1629,11 @@
         <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -3381,11 +3381,11 @@
         <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -3965,11 +3965,11 @@
         <v>8</v>
       </c>
       <c r="E193" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -4549,11 +4549,11 @@
         <v>8</v>
       </c>
       <c r="E225" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         <v>8</v>
       </c>
       <c r="E257" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5717,11 @@
         <v>8</v>
       </c>
       <c r="E289" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6301,11 @@
         <v>8</v>
       </c>
       <c r="E321" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -6885,11 +6885,11 @@
         <v>8</v>
       </c>
       <c r="E353" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7469,11 @@
         <v>8</v>
       </c>
       <c r="E385" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v>8</v>
       </c>
       <c r="E417" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -8637,11 +8637,11 @@
         <v>8</v>
       </c>
       <c r="E449" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -9221,11 +9221,11 @@
         <v>8</v>
       </c>
       <c r="E481" t="n">
-        <v>461</v>
+        <v>478</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9805,11 @@
         <v>8</v>
       </c>
       <c r="E513" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -10389,11 +10389,11 @@
         <v>8</v>
       </c>
       <c r="E545" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -10973,11 +10973,11 @@
         <v>8</v>
       </c>
       <c r="E577" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -11557,11 +11557,11 @@
         <v>8</v>
       </c>
       <c r="E609" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -12141,11 +12141,11 @@
         <v>8</v>
       </c>
       <c r="E641" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -12725,11 +12725,11 @@
         <v>8</v>
       </c>
       <c r="E673" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v>8</v>
       </c>
       <c r="E705" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13893,11 @@
         <v>8</v>
       </c>
       <c r="E737" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -14477,11 +14477,11 @@
         <v>8</v>
       </c>
       <c r="E769" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-08-30 11:36</t>
+          <t>2026-08-31 14:17</t>
         </is>
       </c>
     </row>
@@ -14801,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1024</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="3">
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1230</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="4">
@@ -15007,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>798</v>
+        <v>820</v>
       </c>
     </row>
     <row r="5">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1059</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <v>4326</v>
       </c>
       <c r="AG6" t="n">
-        <v>4111</v>
+        <v>4248</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -11903,7 +11903,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-01 11:21</t>
+          <t>2026-09-02 10:56</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>13</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>12</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>53</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-02 10:56</t>
+          <t>2026-09-03 10:58</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>69</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>221</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-03 10:58</t>
+          <t>2026-09-04 10:54</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>82</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>107</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>332</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-04 10:54</t>
+          <t>2026-09-05 10:09</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>122</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>147</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>100</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>110</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>479</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-05 10:09</t>
+          <t>2026-09-06 10:17</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>168</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>195</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>135</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>145</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>643</v>
+        <v>759</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -11903,7 +11903,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-06 10:17</t>
+          <t>2026-09-07 12:25</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>188</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>218</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>151</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>202</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>759</v>
+        <v>917</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-07 12:25</t>
+          <t>2026-09-08 10:58</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>224</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>252</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>179</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>262</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>917</v>
+        <v>1048</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -14913,7 +14913,7 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-08 10:58</t>
+          <t>2026-09-09 11:03</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>249</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>284</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>206</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>309</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>1048</v>
+        <v>1182</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-09 11:03</t>
+          <t>2026-09-10 10:58</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>276</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>327</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>249</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>330</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>1182</v>
+        <v>1344</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -7685,11 +7685,11 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-10 10:58</t>
+          <t>2026-09-11 10:58</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>321</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>370</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>282</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>371</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>1344</v>
+        <v>1496</v>
       </c>
     </row>
   </sheetData>

--- a/greenlife_scraper/historico_leads.xlsx
+++ b/greenlife_scraper/historico_leads.xlsx
@@ -1063,11 +1063,11 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -1665,11 +1665,11 @@
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3471,11 @@
         <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -4073,11 +4073,11 @@
         <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -4675,11 +4675,11 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,11 @@
         <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5879,11 @@
         <v>9</v>
       </c>
       <c r="E298" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6481,11 @@
         <v>9</v>
       </c>
       <c r="E331" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -7083,11 +7083,11 @@
         <v>9</v>
       </c>
       <c r="E364" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         <v>9</v>
       </c>
       <c r="E430" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -8889,11 +8889,11 @@
         <v>9</v>
       </c>
       <c r="E463" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -9491,11 +9491,11 @@
         <v>9</v>
       </c>
       <c r="E496" t="n">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -10093,11 +10093,11 @@
         <v>9</v>
       </c>
       <c r="E529" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -10695,11 +10695,11 @@
         <v>9</v>
       </c>
       <c r="E562" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>9</v>
       </c>
       <c r="E595" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>9</v>
       </c>
       <c r="E628" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -12501,11 +12501,11 @@
         <v>9</v>
       </c>
       <c r="E661" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -13103,11 +13103,11 @@
         <v>9</v>
       </c>
       <c r="E694" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v>9</v>
       </c>
       <c r="E727" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -14307,11 +14307,11 @@
         <v>9</v>
       </c>
       <c r="E760" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -14909,11 +14909,11 @@
         <v>9</v>
       </c>
       <c r="E793" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-09-11 10:58</t>
+          <t>2026-09-12 10:14</t>
         </is>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>379</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3">
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>412</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>314</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>391</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6">
@@ -15666,7 +15666,7 @@
         <v>4248</v>
       </c>
       <c r="AH6" t="n">
-        <v>1496</v>
+        <v>1616</v>
       </c>
     </row>
   </sheetData>
